--- a/apps/frontend/public/templates/question-bank-template.xlsx
+++ b/apps/frontend/public/templates/question-bank-template.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="QuestionBank" sheetId="1" r:id="rId1"/>
+    <sheet name="Template Tiếng Việt" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -576,4 +577,203 @@
     <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <cols>
+    <col min="1" max="1" width="50.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="24.83203125" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" customWidth="1"/>
+    <col min="11" max="11" width="40.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Câu hỏi</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Loại</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Đáp án A</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Đáp án B</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Đáp án C</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Đáp án D</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Đáp án đúng</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Độ khó</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Thẻ</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Điểm</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Giải thích</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Dòng điện định mức của CB 1 pha 220V là?</v>
+      </c>
+      <c r="B2" t="str">
+        <v>SINGLE_CHOICE</v>
+      </c>
+      <c r="C2" t="str">
+        <v>10A</v>
+      </c>
+      <c r="D2" t="str">
+        <v>16A</v>
+      </c>
+      <c r="E2" t="str">
+        <v>20A</v>
+      </c>
+      <c r="F2" t="str">
+        <v>32A</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Dễ</v>
+      </c>
+      <c r="I2" t="str">
+        <v>điện,cb</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Dòng định mức CB 16A phổ biến cho mạch gia dụng.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>PPE nào bắt buộc khi làm việc trên cao?</v>
+      </c>
+      <c r="B3" t="str">
+        <v>MULTI_CHOICE</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Mũ bảo hộ</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Dây an toàn</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Kính mát</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Giày chống trượt</v>
+      </c>
+      <c r="G3" t="str">
+        <v>A,B,D</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Trung bình</v>
+      </c>
+      <c r="I3" t="str">
+        <v>an toàn,làm việc trên cao</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Kính mát không phải PPE bắt buộc (dùng kính bảo hộ thay thế).</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Đúng hay sai: SCORM là tiêu chuẩn e-learning</v>
+      </c>
+      <c r="B4" t="str">
+        <v>TRUE_FALSE</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>Đúng</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Dễ</v>
+      </c>
+      <c r="I4" t="str">
+        <v>e-learning,tiêu chuẩn</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Viết tắt của "Personal Protective Equipment" là?</v>
+      </c>
+      <c r="B5" t="str">
+        <v>FILL_BLANK</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>PPE,ppe</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Dễ</v>
+      </c>
+      <c r="I5" t="str">
+        <v>ppe,viết tắt</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+  </ignoredErrors>
+</worksheet>
 </file>